--- a/artfynd/A 15455-2025 artfynd.xlsx
+++ b/artfynd/A 15455-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1669,120 +1669,6 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>117708165</v>
-      </c>
-      <c r="B10" t="n">
-        <v>56936</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>102964</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Fiskmås</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Larus canus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Namnlös tjärn Leduskärsvägen, Rovögern, Täftelandet, Vb</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>773282</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7079985</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Maud Tyboni</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Maud Tyboni</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15455-2025 artfynd.xlsx
+++ b/artfynd/A 15455-2025 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>126882633</v>
       </c>
       <c r="B10" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 15455-2025 artfynd.xlsx
+++ b/artfynd/A 15455-2025 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>126882633</v>
       </c>
       <c r="B10" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 15455-2025 artfynd.xlsx
+++ b/artfynd/A 15455-2025 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>126882633</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 15455-2025 artfynd.xlsx
+++ b/artfynd/A 15455-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,6 +1778,129 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134001283</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57263</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Namnlös tjärn Leduskärsvägen, Rovögern, Täftelandet, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>773282</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7079985</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15455-2025 artfynd.xlsx
+++ b/artfynd/A 15455-2025 artfynd.xlsx
@@ -1783,7 +1783,7 @@
         <v>134001283</v>
       </c>
       <c r="B11" t="n">
-        <v>57263</v>
+        <v>57270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 15455-2025 artfynd.xlsx
+++ b/artfynd/A 15455-2025 artfynd.xlsx
@@ -1783,7 +1783,7 @@
         <v>134001283</v>
       </c>
       <c r="B11" t="n">
-        <v>57270</v>
+        <v>57280</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 15455-2025 artfynd.xlsx
+++ b/artfynd/A 15455-2025 artfynd.xlsx
@@ -675,68 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55638746</v>
+        <v>92941753</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103056</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Rovantjärnen, Täftelandet, Vb</t>
+          <t>Namnlös tjärn Leduskärsvägen, Rovögern, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>773423.2362771861</v>
+        <v>773282</v>
       </c>
       <c r="R2" t="n">
-        <v>7080000.384819812</v>
+        <v>7079985</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1991-07-20</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1991-07-20</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Intill norra delen av tjärnen.</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,54 +782,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulf Skyllberg</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulf Skyllberg</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86484433</v>
+        <v>94927542</v>
       </c>
       <c r="B3" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102964</v>
+        <v>100063</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -853,7 +835,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -863,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>773282.0438725457</v>
+        <v>773282</v>
       </c>
       <c r="R3" t="n">
-        <v>7079984.5377855</v>
+        <v>7079985</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,22 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,44 +910,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Maud Tyboni, Maria Zetterström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>92941666</v>
+        <v>94927565</v>
       </c>
       <c r="B4" t="n">
-        <v>55511</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102932</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,15 +950,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -991,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>773282.0438725457</v>
+        <v>773282</v>
       </c>
       <c r="R4" t="n">
-        <v>7079984.5377855</v>
+        <v>7079985</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1021,22 +998,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-01</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,44 +1033,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Maud Tyboni, Maria Zetterström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94927542</v>
+        <v>116936717</v>
       </c>
       <c r="B5" t="n">
-        <v>56099</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100063</v>
+        <v>100067</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1109,7 +1081,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1119,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>773282.0438725457</v>
+        <v>773282</v>
       </c>
       <c r="R5" t="n">
-        <v>7079984.5377855</v>
+        <v>7079985</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1149,22 +1121,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>07:10</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,56 +1146,55 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maud Tyboni, Maria Zetterström</t>
+          <t>Maud Tyboni, Maria Zetterström, Marie Pfrunder</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>94927581</v>
+        <v>92941666</v>
       </c>
       <c r="B6" t="n">
-        <v>55978</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102966</v>
+        <v>102932</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1243,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>773282.0438725457</v>
+        <v>773282</v>
       </c>
       <c r="R6" t="n">
-        <v>7079984.5377855</v>
+        <v>7079985</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1273,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,22 +1269,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maud Tyboni, Maria Zetterström</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94927579</v>
+        <v>117708160</v>
       </c>
       <c r="B7" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57546</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,33 +1287,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103035</v>
+        <v>102963</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1367,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>773282.0438725457</v>
+        <v>773282</v>
       </c>
       <c r="R7" t="n">
-        <v>7079984.5377855</v>
+        <v>7079985</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1397,22 +1353,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-07-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,60 +1378,51 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maud Tyboni, Maria Zetterström</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116936717</v>
+        <v>94927581</v>
       </c>
       <c r="B8" t="n">
-        <v>57194</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>102966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1525,12 +1462,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2021-07-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,22 +1497,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Maud Tyboni, Maria Zetterström, Marie Pfrunder</t>
+          <t>Maud Tyboni, Maria Zetterström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117708160</v>
+        <v>126882633</v>
       </c>
       <c r="B9" t="n">
-        <v>56922</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,49 +1515,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102963</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Namnlös tjärn Leduskärsvägen, Rovögern, Täftelandet, Vb</t>
+          <t>Leduskärsvägen, Rovögern, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>773282</v>
+        <v>773200</v>
       </c>
       <c r="R9" t="n">
-        <v>7079985</v>
+        <v>7079893</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1639,12 +1581,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,32 +1613,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126882633</v>
+        <v>55638746</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>58656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>103056</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1705,26 +1647,29 @@
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Leduskärsvägen, Rovögern, Vb</t>
+          <t>Norra Rovantjärnen, Täftelandet, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>773200</v>
+        <v>773423</v>
       </c>
       <c r="R10" t="n">
-        <v>7079893</v>
+        <v>7080000</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,12 +1693,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>1991-07-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>1991-07-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Intill norra delen av tjärnen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,22 +1728,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Ulf Skyllberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Ulf Skyllberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134001283</v>
+        <v>94927579</v>
       </c>
       <c r="B11" t="n">
-        <v>57280</v>
+        <v>58085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,37 +1751,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100065</v>
+        <v>205976</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1861,22 +1817,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2021-07-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1896,7 +1852,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Maud Tyboni, Maria Zetterström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 15455-2025 artfynd.xlsx
+++ b/artfynd/A 15455-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92941753</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94927542</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94927565</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116936717</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1273,6 +1298,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92941666</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117708160</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94927581</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1610,6 +1650,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126882633</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1737,6 +1782,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55638746</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1856,8 +1906,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94927579</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>